--- a/tasks/finalpool/pw-yf-risk-assessment-excel-ppt/groundtruth_workspace/Risk_Assessment_Report.xlsx
+++ b/tasks/finalpool/pw-yf-risk-assessment-excel-ppt/groundtruth_workspace/Risk_Assessment_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,25 +440,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Current_Price</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Target_Price</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Current_Price</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target_Price</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
@@ -470,23 +460,13 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Amazon.com, Inc.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
+      <c r="B2" t="n">
+        <v>218.94</v>
+      </c>
+      <c r="C2" t="n">
+        <v>240.83</v>
       </c>
       <c r="D2" t="n">
-        <v>218.94</v>
-      </c>
-      <c r="E2" t="n">
-        <v>240.83</v>
-      </c>
-      <c r="F2" t="n">
         <v>21.89</v>
       </c>
     </row>
@@ -496,23 +476,13 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
+      <c r="B3" t="n">
+        <v>300.88</v>
+      </c>
+      <c r="C3" t="n">
+        <v>330.97</v>
       </c>
       <c r="D3" t="n">
-        <v>300.88</v>
-      </c>
-      <c r="E3" t="n">
-        <v>330.97</v>
-      </c>
-      <c r="F3" t="n">
         <v>30.09</v>
       </c>
     </row>
@@ -522,23 +492,13 @@
           <t>JNJ</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
+      <c r="B4" t="n">
+        <v>239.63</v>
+      </c>
+      <c r="C4" t="n">
+        <v>263.59</v>
       </c>
       <c r="D4" t="n">
-        <v>239.63</v>
-      </c>
-      <c r="E4" t="n">
-        <v>263.59</v>
-      </c>
-      <c r="F4" t="n">
         <v>23.96</v>
       </c>
     </row>
@@ -548,23 +508,13 @@
           <t>JPM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JP Morgan Chase &amp; Co.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
+      <c r="B5" t="n">
+        <v>293.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>322.91</v>
       </c>
       <c r="D5" t="n">
-        <v>293.55</v>
-      </c>
-      <c r="E5" t="n">
-        <v>322.91</v>
-      </c>
-      <c r="F5" t="n">
         <v>29.36</v>
       </c>
     </row>
@@ -574,23 +524,13 @@
           <t>XOM</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Exxon Mobil Corporation</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
+      <c r="B6" t="n">
+        <v>150.76</v>
+      </c>
+      <c r="C6" t="n">
+        <v>165.84</v>
       </c>
       <c r="D6" t="n">
-        <v>150.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>165.84</v>
-      </c>
-      <c r="F6" t="n">
         <v>15.08</v>
       </c>
     </row>
@@ -663,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,11 +617,6 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -692,11 +627,6 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -705,11 +635,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Hold</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>XOM</t>
         </is>
       </c>
     </row>
